--- a/artfynd/A 11545-2022 artfynd.xlsx
+++ b/artfynd/A 11545-2022 artfynd.xlsx
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134361768</v>
+        <v>134362228</v>
       </c>
       <c r="B2" t="n">
-        <v>99181</v>
+        <v>80474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465943</v>
+        <v>465962</v>
       </c>
       <c r="R2" t="n">
-        <v>6890678</v>
+        <v>6890718</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,48 +772,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134362228</v>
+        <v>134361768</v>
       </c>
       <c r="B3" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465962</v>
+        <v>465943</v>
       </c>
       <c r="R3" t="n">
-        <v>6890718</v>
+        <v>6890678</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134361319</v>
+        <v>134363040</v>
       </c>
       <c r="B16" t="n">
-        <v>80475</v>
+        <v>80474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465929</v>
+        <v>466056</v>
       </c>
       <c r="R16" t="n">
-        <v>6890708</v>
+        <v>6890848</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134362681</v>
+        <v>134360670</v>
       </c>
       <c r="B17" t="n">
-        <v>80474</v>
+        <v>80475</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,21 +2177,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465965</v>
+        <v>465936</v>
       </c>
       <c r="R17" t="n">
-        <v>6890827</v>
+        <v>6890807</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134363040</v>
+        <v>134362681</v>
       </c>
       <c r="B18" t="n">
         <v>80474</v>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466056</v>
+        <v>465965</v>
       </c>
       <c r="R18" t="n">
-        <v>6890848</v>
+        <v>6890827</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134360670</v>
+        <v>134361319</v>
       </c>
       <c r="B20" t="n">
         <v>80475</v>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465936</v>
+        <v>465929</v>
       </c>
       <c r="R20" t="n">
-        <v>6890807</v>
+        <v>6890708</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2845,32 +2845,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134361493</v>
+        <v>134361259</v>
       </c>
       <c r="B24" t="n">
-        <v>99181</v>
+        <v>80479</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465918</v>
+        <v>465910</v>
       </c>
       <c r="R24" t="n">
-        <v>6890701</v>
+        <v>6890716</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2942,32 +2942,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134361259</v>
+        <v>134361493</v>
       </c>
       <c r="B25" t="n">
-        <v>80479</v>
+        <v>99181</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465910</v>
+        <v>465918</v>
       </c>
       <c r="R25" t="n">
-        <v>6890716</v>
+        <v>6890701</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3039,32 +3039,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134360648</v>
+        <v>134360684</v>
       </c>
       <c r="B26" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465940</v>
+        <v>465931</v>
       </c>
       <c r="R26" t="n">
-        <v>6890813</v>
+        <v>6890799</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134360625</v>
+        <v>134360648</v>
       </c>
       <c r="B27" t="n">
-        <v>58136</v>
+        <v>80474</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,46 +3147,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465932</v>
+        <v>465940</v>
       </c>
       <c r="R27" t="n">
-        <v>6890803</v>
+        <v>6890813</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3242,48 +3233,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134360684</v>
+        <v>134360625</v>
       </c>
       <c r="B28" t="n">
-        <v>99181</v>
+        <v>58136</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465931</v>
+        <v>465932</v>
       </c>
       <c r="R28" t="n">
-        <v>6890799</v>
+        <v>6890803</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3736,45 +3736,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134363138</v>
+        <v>134361245</v>
       </c>
       <c r="B33" t="n">
-        <v>99203</v>
+        <v>99181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466043</v>
+        <v>465911</v>
       </c>
       <c r="R33" t="n">
-        <v>6890871</v>
+        <v>6890723</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3833,54 +3842,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134361245</v>
+        <v>134363138</v>
       </c>
       <c r="B34" t="n">
-        <v>99181</v>
+        <v>99203</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465911</v>
+        <v>466043</v>
       </c>
       <c r="R34" t="n">
-        <v>6890723</v>
+        <v>6890871</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>

--- a/artfynd/A 11545-2022 artfynd.xlsx
+++ b/artfynd/A 11545-2022 artfynd.xlsx
@@ -675,48 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134362228</v>
+        <v>134361768</v>
       </c>
       <c r="B2" t="n">
-        <v>80474</v>
+        <v>99188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465962</v>
+        <v>465943</v>
       </c>
       <c r="R2" t="n">
-        <v>6890718</v>
+        <v>6890678</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,57 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134361768</v>
+        <v>134362228</v>
       </c>
       <c r="B3" t="n">
-        <v>99181</v>
+        <v>80481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465943</v>
+        <v>465962</v>
       </c>
       <c r="R3" t="n">
-        <v>6890678</v>
+        <v>6890718</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>134360640</v>
       </c>
       <c r="B4" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>134361161</v>
       </c>
       <c r="B5" t="n">
-        <v>80486</v>
+        <v>80493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>134362151</v>
       </c>
       <c r="B6" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>134361658</v>
       </c>
       <c r="B7" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>134360940</v>
       </c>
       <c r="B8" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>134362771</v>
       </c>
       <c r="B9" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>134362932</v>
       </c>
       <c r="B10" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>134361431</v>
       </c>
       <c r="B11" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>134360805</v>
       </c>
       <c r="B12" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>134361101</v>
       </c>
       <c r="B13" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>134362205</v>
       </c>
       <c r="B14" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>134361955</v>
       </c>
       <c r="B15" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134363040</v>
+        <v>134361319</v>
       </c>
       <c r="B16" t="n">
-        <v>80474</v>
+        <v>80482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>466056</v>
+        <v>465929</v>
       </c>
       <c r="R16" t="n">
-        <v>6890848</v>
+        <v>6890708</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134360670</v>
+        <v>134362681</v>
       </c>
       <c r="B17" t="n">
-        <v>80475</v>
+        <v>80481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,21 +2177,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465936</v>
+        <v>465965</v>
       </c>
       <c r="R17" t="n">
-        <v>6890807</v>
+        <v>6890827</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134362681</v>
+        <v>134363040</v>
       </c>
       <c r="B18" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465965</v>
+        <v>466056</v>
       </c>
       <c r="R18" t="n">
-        <v>6890827</v>
+        <v>6890848</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2363,7 +2363,7 @@
         <v>134362956</v>
       </c>
       <c r="B19" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134361319</v>
+        <v>134360670</v>
       </c>
       <c r="B20" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465929</v>
+        <v>465936</v>
       </c>
       <c r="R20" t="n">
-        <v>6890708</v>
+        <v>6890807</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2557,7 +2557,7 @@
         <v>134360820</v>
       </c>
       <c r="B21" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,10 +2651,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134362194</v>
+        <v>134362532</v>
       </c>
       <c r="B22" t="n">
-        <v>80474</v>
+        <v>58136</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2662,21 +2662,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465972</v>
+        <v>465986</v>
       </c>
       <c r="R22" t="n">
-        <v>6890718</v>
+        <v>6890782</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2748,10 +2748,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134362532</v>
+        <v>134362194</v>
       </c>
       <c r="B23" t="n">
-        <v>58136</v>
+        <v>80481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2759,21 +2759,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465986</v>
+        <v>465972</v>
       </c>
       <c r="R23" t="n">
-        <v>6890782</v>
+        <v>6890718</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2845,32 +2845,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134361259</v>
+        <v>134361493</v>
       </c>
       <c r="B24" t="n">
-        <v>80479</v>
+        <v>99188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465910</v>
+        <v>465918</v>
       </c>
       <c r="R24" t="n">
-        <v>6890716</v>
+        <v>6890701</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2942,32 +2942,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134361493</v>
+        <v>134361259</v>
       </c>
       <c r="B25" t="n">
-        <v>99181</v>
+        <v>80486</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465918</v>
+        <v>465910</v>
       </c>
       <c r="R25" t="n">
-        <v>6890701</v>
+        <v>6890716</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3039,32 +3039,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134360684</v>
+        <v>134360648</v>
       </c>
       <c r="B26" t="n">
-        <v>99181</v>
+        <v>80481</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465931</v>
+        <v>465940</v>
       </c>
       <c r="R26" t="n">
-        <v>6890799</v>
+        <v>6890813</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134360648</v>
+        <v>134360625</v>
       </c>
       <c r="B27" t="n">
-        <v>80474</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,37 +3147,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465940</v>
+        <v>465932</v>
       </c>
       <c r="R27" t="n">
-        <v>6890813</v>
+        <v>6890803</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3233,57 +3242,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134360625</v>
+        <v>134360684</v>
       </c>
       <c r="B28" t="n">
-        <v>58136</v>
+        <v>99188</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465932</v>
+        <v>465931</v>
       </c>
       <c r="R28" t="n">
-        <v>6890803</v>
+        <v>6890799</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>134360877</v>
       </c>
       <c r="B29" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>134361201</v>
       </c>
       <c r="B30" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>134362606</v>
       </c>
       <c r="B31" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3639,32 +3639,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134363102</v>
+        <v>134363138</v>
       </c>
       <c r="B32" t="n">
-        <v>80475</v>
+        <v>99210</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3674,13 +3674,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466060</v>
+        <v>466043</v>
       </c>
       <c r="R32" t="n">
-        <v>6890849</v>
+        <v>6890871</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>134361245</v>
       </c>
       <c r="B33" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3842,32 +3842,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134363138</v>
+        <v>134363102</v>
       </c>
       <c r="B34" t="n">
-        <v>99203</v>
+        <v>80482</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466043</v>
+        <v>466060</v>
       </c>
       <c r="R34" t="n">
-        <v>6890871</v>
+        <v>6890849</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 11545-2022 artfynd.xlsx
+++ b/artfynd/A 11545-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134361768</v>
+        <v>134360670</v>
       </c>
       <c r="B2" t="n">
-        <v>99188</v>
+        <v>80489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465943</v>
+        <v>465936</v>
       </c>
       <c r="R2" t="n">
-        <v>6890678</v>
+        <v>6890807</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -781,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134362228</v>
+        <v>134361319</v>
       </c>
       <c r="B3" t="n">
-        <v>80481</v>
+        <v>80489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465962</v>
+        <v>465929</v>
       </c>
       <c r="R3" t="n">
-        <v>6890718</v>
+        <v>6890708</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,57 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134360640</v>
+        <v>134362205</v>
       </c>
       <c r="B4" t="n">
-        <v>99188</v>
+        <v>80489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465942</v>
+        <v>465970</v>
       </c>
       <c r="R4" t="n">
-        <v>6890820</v>
+        <v>6890728</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134361161</v>
+        <v>134362606</v>
       </c>
       <c r="B5" t="n">
-        <v>80493</v>
+        <v>80489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1019,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465891</v>
+        <v>465951</v>
       </c>
       <c r="R5" t="n">
-        <v>6890722</v>
+        <v>6890810</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1081,54 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134362151</v>
+        <v>134363102</v>
       </c>
       <c r="B6" t="n">
-        <v>99188</v>
+        <v>80489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465977</v>
+        <v>466060</v>
       </c>
       <c r="R6" t="n">
-        <v>6890698</v>
+        <v>6890849</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1187,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134361658</v>
+        <v>134361431</v>
       </c>
       <c r="B7" t="n">
-        <v>83351</v>
+        <v>83358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1222,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465946</v>
+        <v>465934</v>
       </c>
       <c r="R7" t="n">
-        <v>6890675</v>
+        <v>6890719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134360940</v>
+        <v>134361658</v>
       </c>
       <c r="B8" t="n">
-        <v>99092</v>
+        <v>83358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220093</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465880</v>
+        <v>465946</v>
       </c>
       <c r="R8" t="n">
-        <v>6890725</v>
+        <v>6890675</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134362771</v>
+        <v>134361955</v>
       </c>
       <c r="B9" t="n">
-        <v>99210</v>
+        <v>83358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1416,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465988</v>
+        <v>465955</v>
       </c>
       <c r="R9" t="n">
-        <v>6890774</v>
+        <v>6890673</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1478,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134362932</v>
+        <v>134361822</v>
       </c>
       <c r="B10" t="n">
-        <v>80481</v>
+        <v>79130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466026</v>
+        <v>465940</v>
       </c>
       <c r="R10" t="n">
-        <v>6890811</v>
+        <v>6890662</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1575,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134361431</v>
+        <v>134360648</v>
       </c>
       <c r="B11" t="n">
-        <v>83351</v>
+        <v>80488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1610,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465934</v>
+        <v>465940</v>
       </c>
       <c r="R11" t="n">
-        <v>6890719</v>
+        <v>6890813</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1672,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134360805</v>
+        <v>134362194</v>
       </c>
       <c r="B12" t="n">
-        <v>99210</v>
+        <v>80488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1707,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465909</v>
+        <v>465972</v>
       </c>
       <c r="R12" t="n">
-        <v>6890760</v>
+        <v>6890718</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1769,57 +1742,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134361101</v>
+        <v>134362228</v>
       </c>
       <c r="B13" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465897</v>
+        <v>465962</v>
       </c>
       <c r="R13" t="n">
-        <v>6890701</v>
+        <v>6890718</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1875,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134362205</v>
+        <v>134362681</v>
       </c>
       <c r="B14" t="n">
-        <v>80482</v>
+        <v>80488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1910,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465970</v>
+        <v>465965</v>
       </c>
       <c r="R14" t="n">
-        <v>6890728</v>
+        <v>6890827</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1972,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134361955</v>
+        <v>134362932</v>
       </c>
       <c r="B15" t="n">
-        <v>83351</v>
+        <v>80488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2007,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465955</v>
+        <v>466026</v>
       </c>
       <c r="R15" t="n">
-        <v>6890673</v>
+        <v>6890811</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2069,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134361319</v>
+        <v>134362956</v>
       </c>
       <c r="B16" t="n">
-        <v>80482</v>
+        <v>80488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2104,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465929</v>
+        <v>466034</v>
       </c>
       <c r="R16" t="n">
-        <v>6890708</v>
+        <v>6890831</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2166,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134362681</v>
+        <v>134363040</v>
       </c>
       <c r="B17" t="n">
-        <v>80481</v>
+        <v>80488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465965</v>
+        <v>466056</v>
       </c>
       <c r="R17" t="n">
-        <v>6890827</v>
+        <v>6890848</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2263,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134363040</v>
+        <v>134361259</v>
       </c>
       <c r="B18" t="n">
-        <v>80481</v>
+        <v>80493</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466056</v>
+        <v>465910</v>
       </c>
       <c r="R18" t="n">
-        <v>6890848</v>
+        <v>6890716</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2360,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134362956</v>
+        <v>134361161</v>
       </c>
       <c r="B19" t="n">
-        <v>80481</v>
+        <v>80500</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2395,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466034</v>
+        <v>465891</v>
       </c>
       <c r="R19" t="n">
-        <v>6890831</v>
+        <v>6890722</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2457,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134360670</v>
+        <v>134360625</v>
       </c>
       <c r="B20" t="n">
-        <v>80482</v>
+        <v>58136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2468,34 +2432,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465936</v>
+        <v>465932</v>
       </c>
       <c r="R20" t="n">
-        <v>6890807</v>
+        <v>6890803</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2554,32 +2527,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134360820</v>
+        <v>134362532</v>
       </c>
       <c r="B21" t="n">
-        <v>99092</v>
+        <v>58136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220093</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2589,13 +2562,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465909</v>
+        <v>465986</v>
       </c>
       <c r="R21" t="n">
-        <v>6890754</v>
+        <v>6890782</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2651,32 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134362532</v>
+        <v>134360820</v>
       </c>
       <c r="B22" t="n">
-        <v>58136</v>
+        <v>99099</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220093</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2686,13 +2659,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465986</v>
+        <v>465909</v>
       </c>
       <c r="R22" t="n">
-        <v>6890782</v>
+        <v>6890754</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2748,32 +2721,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134362194</v>
+        <v>134360877</v>
       </c>
       <c r="B23" t="n">
-        <v>80481</v>
+        <v>99099</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2783,7 +2756,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465972</v>
+        <v>465884</v>
       </c>
       <c r="R23" t="n">
         <v>6890718</v>
@@ -2845,32 +2818,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134361493</v>
+        <v>134360940</v>
       </c>
       <c r="B24" t="n">
-        <v>99188</v>
+        <v>99099</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2880,10 +2853,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465918</v>
+        <v>465880</v>
       </c>
       <c r="R24" t="n">
-        <v>6890701</v>
+        <v>6890725</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2942,48 +2915,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134361259</v>
+        <v>134360640</v>
       </c>
       <c r="B25" t="n">
-        <v>80486</v>
+        <v>99195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>465910</v>
+        <v>465942</v>
       </c>
       <c r="R25" t="n">
-        <v>6890716</v>
+        <v>6890820</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3039,32 +3021,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134360648</v>
+        <v>134360684</v>
       </c>
       <c r="B26" t="n">
-        <v>80481</v>
+        <v>99195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,13 +3056,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>465940</v>
+        <v>465931</v>
       </c>
       <c r="R26" t="n">
-        <v>6890813</v>
+        <v>6890799</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3136,42 +3118,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134360625</v>
+        <v>134361101</v>
       </c>
       <c r="B27" t="n">
-        <v>58136</v>
+        <v>99195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3180,13 +3162,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>465932</v>
+        <v>465897</v>
       </c>
       <c r="R27" t="n">
-        <v>6890803</v>
+        <v>6890701</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3242,10 +3224,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134360684</v>
+        <v>134361201</v>
       </c>
       <c r="B28" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3270,20 +3252,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465931</v>
+        <v>465897</v>
       </c>
       <c r="R28" t="n">
-        <v>6890799</v>
+        <v>6890705</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3339,48 +3330,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134360877</v>
+        <v>134361245</v>
       </c>
       <c r="B29" t="n">
-        <v>99092</v>
+        <v>99195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>465884</v>
+        <v>465911</v>
       </c>
       <c r="R29" t="n">
-        <v>6890718</v>
+        <v>6890723</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134361201</v>
+        <v>134361493</v>
       </c>
       <c r="B30" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3464,29 +3464,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>465897</v>
+        <v>465918</v>
       </c>
       <c r="R30" t="n">
-        <v>6890705</v>
+        <v>6890701</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3542,45 +3533,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134362606</v>
+        <v>134361768</v>
       </c>
       <c r="B31" t="n">
-        <v>80482</v>
+        <v>99195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465951</v>
+        <v>465943</v>
       </c>
       <c r="R31" t="n">
-        <v>6890810</v>
+        <v>6890678</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3639,48 +3639,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134363138</v>
+        <v>134362151</v>
       </c>
       <c r="B32" t="n">
-        <v>99210</v>
+        <v>99195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466043</v>
+        <v>465977</v>
       </c>
       <c r="R32" t="n">
-        <v>6890871</v>
+        <v>6890698</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3736,57 +3745,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134361245</v>
+        <v>134360805</v>
       </c>
       <c r="B33" t="n">
-        <v>99188</v>
+        <v>99217</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Furuhösen, Furuhösen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465911</v>
+        <v>465909</v>
       </c>
       <c r="R33" t="n">
-        <v>6890723</v>
+        <v>6890760</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3842,32 +3842,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134363102</v>
+        <v>134362771</v>
       </c>
       <c r="B34" t="n">
-        <v>80482</v>
+        <v>99217</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3877,13 +3877,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466060</v>
+        <v>465988</v>
       </c>
       <c r="R34" t="n">
-        <v>6890849</v>
+        <v>6890774</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3936,6 +3936,103 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134363138</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Furuhösen, Furuhösen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>466043</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6890871</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11545-2022 artfynd.xlsx
+++ b/artfynd/A 11545-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360670</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134361319</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362205</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362606</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134363102</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134361431</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134361658</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134361955</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134361822</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360648</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362194</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362228</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362681</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362932</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362956</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134363040</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134361259</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134361161</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360625</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362532</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360820</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2815,6 +2925,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360877</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2912,6 +3027,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360940</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3018,6 +3138,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360640</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3115,6 +3240,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360684</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3221,6 +3351,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134361101</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3327,6 +3462,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134361201</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3433,6 +3573,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134361245</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3530,6 +3675,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134361493</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3636,6 +3786,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134361768</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3742,6 +3897,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362151</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3839,6 +3999,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134360805</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3936,6 +4101,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362771</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4033,8 +4203,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134363138</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>